--- a/www/download/COUNTRY.EST.WIOD13.xlsx
+++ b/www/download/COUNTRY.EST.WIOD13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Estônia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.732069749249581</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.765421279197398</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.886257639375243</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.898319147140311</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.936829544846575</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.08150198965166</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1.12067421581635</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1.05838024669571</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.884040373180654</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.804181745990278</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.803019327628949</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.795988246201261</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.729713971652249</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.680147068595328</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.717622186357779</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>1.8178174588626</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>1.62378647153876</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>1.52461460764054</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>1.31517812808268</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>1.25870758220275</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>0.971128612458655</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>1.04303864863199</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>0.669736414452915</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>0.488937277643452</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>0.408991035620016</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>0.556287252274289</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>0.610529982453126</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>0.638359074276649</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.524201620459688</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>0.622192579718947</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>3.96445870352701</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>3.57660166595455</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>3.34618355634921</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>3.0642741199111</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>3.16430529316012</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.521</t>
+          <t>2.63897847087112</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>2.51785561908581</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>1.83300684471784</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.542</t>
+          <t>1.40189574530336</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>1.3245368691604</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>1.5578582012179</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>1.61951554884636</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>1.43168521877227</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>1.23571375474286</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>1.31650106722806</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1229.997</t>
+          <t>5.46372962840936</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1202.232</t>
+          <t>4.93949280445424</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1197.109</t>
+          <t>4.68652787648493</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1175.736</t>
+          <t>4.28583707573947</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1121.586</t>
+          <t>4.59389780311722</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1108.908</t>
+          <t>3.92192706560602</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1114.127</t>
+          <t>3.7339293960915</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1127.774</t>
+          <t>2.73460664373642</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1148.49</t>
+          <t>1.36382846157049</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1152.113</t>
+          <t>2.04648282228669</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1185.772</t>
+          <t>2.23227845379126</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1259.874</t>
+          <t>2.16712853883862</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1271.582</t>
+          <t>1.68057921287284</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1270.92</t>
+          <t>1.28385641988462</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1097.816</t>
+          <t>1.40236183698293</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1102.698</t>
+          <t>1431893170.5968</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1071.376</t>
+          <t>1384128329.83909</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1064.047</t>
+          <t>1444451542.17918</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1038.062</t>
+          <t>1471242867.14041</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>992.222</t>
+          <t>1383914729.87237</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>975.926</t>
+          <t>1468464924.29296</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>995.82</t>
+          <t>1587507446.66584</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1009.111</t>
+          <t>1667484534.71359</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1022.755</t>
+          <t>1768722106.5545</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1018.847</t>
+          <t>1884345214.63199</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1073.443</t>
+          <t>1742779742.54585</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1141.254</t>
+          <t>1785700290.13512</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1140.255</t>
+          <t>1661334362.14886</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1141.369</t>
+          <t>1592164302.90374</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>952.965</t>
+          <t>1293742272.14713</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>274811149.068064</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>42.43</t>
+          <t>288442271.662237</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>297425235.964501</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>309931465.833519</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>293887935.379961</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>39.63</t>
+          <t>330596747.151728</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>39.19</t>
+          <t>341593574.251427</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>429854851.804465</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>35.89</t>
+          <t>509924272.743985</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>523459619.868147</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>507583789.578934</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>522701403.122937</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>542821711.213754</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>591833200.674104</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>38.97</t>
+          <t>478141919.206822</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>49.58</t>
+          <t>6341849.4716636</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>50.53</t>
+          <t>5240079.99986205</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>50.76</t>
+          <t>5364297.80524225</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>51.03</t>
+          <t>4488653.56372391</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>53.04</t>
+          <t>4148846.41557092</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>52.96</t>
+          <t>4191576.39662423</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>53.46</t>
+          <t>4095587.58329891</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>3637257.06777023</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>53.21</t>
+          <t>2965715.52171097</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>52.54</t>
+          <t>2644320.6812522</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>2182875.4981895</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>50.66</t>
+          <t>1892391.59245988</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>53.01</t>
+          <t>1453884.44129711</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>52.78</t>
+          <t>1285085.59547857</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>52.36</t>
+          <t>1373274.72572533</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>6088.87671723142</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>5906.94238817744</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.82</t>
+          <t>5771.48510203149</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>5547.81248410525</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>5276.1507520347</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>5308.13989046519</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>5254.12059341404</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>5333.81733216831</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>6013.76074193333</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>6829.42418444583</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7258.15944196673</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>8070.10857599595</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>9289.79526875552</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>10080.0383885284</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7792.56582362023</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>11147.6793270204</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>10855.9328210472</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>11256.3017833092</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>11402.1885284278</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>27.97</t>
+          <t>10958.2860872872</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>12098.3423123363</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>12736.3824002911</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>29.21</t>
+          <t>13676.5001623141</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>28.54</t>
+          <t>15626.1210763378</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>18346.5318184203</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>18172.889064758</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>31.31</t>
+          <t>19515.3709498958</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>20540.1124513495</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>21793.417582923</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>16518.3716721394</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>58.15</t>
+          <t>3.01256768261564</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>58.86</t>
+          <t>2.71435059374569</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>2.5775262344942</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>58.73</t>
+          <t>2.34932746255004</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>60.77</t>
+          <t>2.37619102811299</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>1.9520130564143</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>60.79</t>
+          <t>1.9152175004044</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>1.34756215676968</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>60.02</t>
+          <t>1.00569894917218</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>59.31</t>
+          <t>0.946372632337393</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>58.51</t>
+          <t>1.11481010433858</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>57.67</t>
+          <t>1.1833772861168</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>58.67</t>
+          <t>1.10060632939046</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>57.98</t>
+          <t>0.928531171789567</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>57.62</t>
+          <t>0.993058048985329</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>965.288169519933</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>1095.15629747023</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>1129.11350004515</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>1155.65720552426</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>11.26</t>
+          <t>1377.25679093992</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>1215.3883204992</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>1571.473950914</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>1514.93878962717</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>11.44</t>
+          <t>2033.60220674006</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>2513.15929087079</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>2519.15435837949</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>3114.35149290779</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>3917.10466677892</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>4272.65347475342</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>3778.40567452188</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.732069749249581</t>
+          <t>465.860568008246</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.765421279197398</t>
+          <t>503.389653860797</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.886257639375243</t>
+          <t>523.175437052772</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.898319147140311</t>
+          <t>559.03944053665</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.936829544846575</t>
+          <t>554.819587275743</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08150198965166</t>
+          <t>634.786380859693</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.12067421581635</t>
+          <t>644.759483486611</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05838024669571</t>
+          <t>798.541429312124</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884040373180654</t>
+          <t>941.340728713282</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.804181745990278</t>
+          <t>973.154155534167</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803019327628949</t>
+          <t>908.671302504358</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.795988246201261</t>
+          <t>878.637424063634</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729713971652249</t>
+          <t>909.096819854872</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.680147068595328</t>
+          <t>976.622443356607</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.717622186357779</t>
+          <t>874.227842038235</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-208662052.908143</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-162914901.567079</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-87274097.0213033</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-40167694.6146474</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>11253822.7290866</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>143114252.602462</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>191214590.373285</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>311590669.006368</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>400360242.60465</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>334972065.344363</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>246902992.214156</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>280205929.655199</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>284780083.572726</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>329460234.996629</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>304141705.555734</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-220016324.332616</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-175450005.130579</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-109981574.162083</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-68358272.0027774</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-17495423.9253466</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>95255602.7066761</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>136777321.993518</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>263721003.248133</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>335478622.016353</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>252024889.037256</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>165455629.611522</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>199417926.050937</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>195463059.033831</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>228518936.5901</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>198731057.110067</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>11354271.424473</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>12535103.5634998</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>22707477.1407799</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>28190577.3881301</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>28749246.6544332</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>47858649.8957862</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>54437268.3797667</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>47869665.758235</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>64881620.5882962</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>82947176.3071075</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>81447362.6026341</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>80788003.6042618</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>89317024.538895</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>100941298.406529</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>105410648.445666</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1869.29705979486</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1869.76565970329</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1871.67385129926</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1872.40615083801</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1873.17691278171</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1873.8976843318</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1879.61412981187</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1874.62564006591</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1888.04611039321</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1894.12061537711</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1921.66725205872</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>1918.39699443271</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>1909.65453381588</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>1883.44682508251</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>1742.38683722138</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1942.20213950133</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1941.27484554757</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1939.57975752227</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1939.19790711211</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1936.43963717724</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1936.95668820961</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1928.55717842946</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1926.82998291474</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1933.48513636364</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1935.34909964934</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1951.24601941748</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1950.26993498452</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1939.57054939662</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1924.39742818469</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1787.50155921495</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>181.74</t>
+          <t>2167.32849127726</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>162.34</t>
+          <t>2402.29795269921</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>152.44</t>
+          <t>3067.4347138352</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>131.51</t>
+          <t>3484.31085948467</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>129.41</t>
+          <t>3304.5635402525</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>97.08</t>
+          <t>3801.3332003363</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>104.24</t>
+          <t>4159.16409014369</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>66.95</t>
+          <t>4530.15671550546</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>5826.2280084372</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>40.84</t>
+          <t>6741.41451549769</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>55.62</t>
+          <t>8072.00373214941</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>10009.0881723028</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>63.82</t>
+          <t>11380.2511355507</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>52.41</t>
+          <t>13084.9625879172</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>62.21</t>
+          <t>9918.3978810616</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>396.37</t>
+          <t>454662053.505552</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>357.59</t>
+          <t>422472423.645013</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>334.59</t>
+          <t>481845603.337102</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>306.42</t>
+          <t>525060505.854983</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>322.95</t>
+          <t>508550106.552831</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>263.84</t>
+          <t>576321943.691198</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>251.67</t>
+          <t>634357810.836376</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>183.26</t>
+          <t>646011026.630525</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>140.11</t>
+          <t>690556863.093739</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>132.35</t>
+          <t>690340119.28017</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>155.77</t>
+          <t>688142048.790504</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>161.9</t>
+          <t>702351903.24606</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>143.14</t>
+          <t>609163252.183111</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>123.55</t>
+          <t>611431661.806358</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>131.63</t>
+          <t>482014111.378089</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>546.28</t>
+          <t>2546.41826961884</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>493.86</t>
+          <t>3144.99158132517</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>468.61</t>
+          <t>3766.49048932949</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>428.57</t>
+          <t>4203.4508560095</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>468.15</t>
+          <t>3740.89327521901</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>392.11</t>
+          <t>4096.48530438498</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>373.24</t>
+          <t>4409.5318070429</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>5149.8336042185</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>6606.27502048523</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>204.51</t>
+          <t>7725.70451545724</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>223.21</t>
+          <t>9115.80558120576</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>216.65</t>
+          <t>11651.0849010892</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>168.03</t>
+          <t>13466.3510619339</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>128.37</t>
+          <t>13935.8799653936</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>140.22</t>
+          <t>8832.51443366737</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1229.997</t>
+          <t>304530816.210992</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1202.232</t>
+          <t>369636242.37767</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1197.109</t>
+          <t>490231520.412123</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1175.736</t>
+          <t>588490297.804191</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1121.586</t>
+          <t>585423829.746879</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1108.908</t>
+          <t>763250943.591768</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1114.127</t>
+          <t>864649210.361944</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1127.774</t>
+          <t>1053233933.26268</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1148.49</t>
+          <t>1204504912.94953</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1152.113</t>
+          <t>1156754633.30289</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1185.772</t>
+          <t>1064243212.96252</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1259.874</t>
+          <t>1167946972.73687</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1271.582</t>
+          <t>1101580656.00696</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1270.92</t>
+          <t>1015859980.2506</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1097.816</t>
+          <t>680955079.989156</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1102.698</t>
+          <t>-379.089778341575</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1071.376</t>
+          <t>-742.693628625958</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1064.047</t>
+          <t>-699.055775494291</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1038.062</t>
+          <t>-719.139996524834</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>992.222</t>
+          <t>-436.329734966514</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>975.926</t>
+          <t>-295.152104048683</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>995.82</t>
+          <t>-250.367716899219</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1009.111</t>
+          <t>-619.676888713043</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1022.755</t>
+          <t>-780.047012048033</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1018.847</t>
+          <t>-984.289999959545</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1073.443</t>
+          <t>-1043.80184905636</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1141.254</t>
+          <t>-1641.99672878638</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1140.255</t>
+          <t>-2086.09992638326</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1141.369</t>
+          <t>-850.91737747648</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>952.965</t>
+          <t>1085.88344739423</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1432.066</t>
+          <t>150131237.29456</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1384.266</t>
+          <t>52836181.2673429</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1444.538</t>
+          <t>-8385917.07502096</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1471.272</t>
+          <t>-63429791.9492083</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1364.366</t>
+          <t>-76873723.1940475</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1468.711</t>
+          <t>-186928999.900569</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1588.26</t>
+          <t>-230291399.525568</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1667.877</t>
+          <t>-407222906.632156</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1769.693</t>
+          <t>-513948049.855793</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1885.797</t>
+          <t>-466414514.022719</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1742.976</t>
+          <t>-376101164.172015</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1786.424</t>
+          <t>-465595069.490813</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1661.53</t>
+          <t>-492417403.823846</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1592.359</t>
+          <t>-404428318.444246</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1293.876</t>
+          <t>-198940968.611068</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1793.59452</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2140.72685</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2215.72546</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2430.87755</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2345.39238</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>2334.89037</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>2549.4012</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>2967.99712</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>3989.60685</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>4725.43966</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>5473.89979</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>6631.53529</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>8560.62565</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>9439.11782</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>7172.98768</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>782.102</t>
+          <t>0.0132931275325453</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>753.133</t>
+          <t>0.0286130789297615</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>740.619</t>
+          <t>0.0373700505807489</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>715.843</t>
+          <t>0.0510412848310967</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>666.322</t>
+          <t>0.0477055315187333</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>644.288</t>
+          <t>0.0611780559910412</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>654.892</t>
+          <t>0.0531364156917896</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>650.317</t>
+          <t>0.0707654428406236</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>680.698</t>
+          <t>0.0707172660597393</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>701.44</t>
+          <t>0.0631200553137523</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>696.057</t>
+          <t>0.0815364116330038</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>738.433</t>
+          <t>0.0755251147651964</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>751.381</t>
+          <t>0.0654863590524271</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>736.419</t>
+          <t>0.0468331485058506</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>610.325</t>
+          <t>0.0241353207873132</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1978.1820783021</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2362.18888529114</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2442.55657145964</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2664.76063660272</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2648.09972342715</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2575.89638618198</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2771.60707940775</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>3248.67343257762</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>4366.19409573783</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>5336.24859621905</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6151.02077167553</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7459.21239006176</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10097.8506948805</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>12308.5231619955</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>10312.433995032</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>274.853</t>
+          <t>2163.1993614518</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>288.486</t>
+          <t>2598.52951763284</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>297.446</t>
+          <t>2685.60327370236</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>309.941</t>
+          <t>2952.21889994261</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>289.357</t>
+          <t>2924.45257344085</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>330.65</t>
+          <t>2873.44566883691</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>341.704</t>
+          <t>3049.05306926796</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>429.922</t>
+          <t>3570.04041898114</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>510.098</t>
+          <t>4873.65566729071</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>523.693</t>
+          <t>6061.3972959849</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>507.615</t>
+          <t>6760.24191490913</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>522.81</t>
+          <t>8225.85810822455</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>542.877</t>
+          <t>11192.336567059</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>591.877</t>
+          <t>13653.5984685896</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>478.176</t>
+          <t>11402.7682049438</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>301.2</t>
+          <t>15075.3469067108</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>271.38</t>
+          <t>16688.5233172253</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>257.73</t>
+          <t>16250.6814097098</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>234.92</t>
+          <t>17142.8042501008</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>242.91</t>
+          <t>17576.1241710507</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>195.15</t>
+          <t>16366.7523337209</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>191.43</t>
+          <t>17744.8560943062</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>134.72</t>
+          <t>20493.0261604917</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>26825.4155126232</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>94.55</t>
+          <t>32943.4903503841</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>111.47</t>
+          <t>37326.934013361</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>118.29</t>
+          <t>45488.4342718116</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>110.04</t>
+          <t>58978.9093797376</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>92.84</t>
+          <t>66640.7588690546</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>99.29</t>
+          <t>62017.4964204802</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>6.343</t>
+          <t>2163.1993614518</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5.241</t>
+          <t>2208.17303224124</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>5.365</t>
+          <t>2391.50829736382</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4.489</t>
+          <t>2510.25849967421</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4.075</t>
+          <t>2402.04956346056</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.192</t>
+          <t>2650.79965257279</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4.098</t>
+          <t>2756.25269208334</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3.638</t>
+          <t>2965.24729246084</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.967</t>
+          <t>3230.77354530927</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.646</t>
+          <t>3571.51776746887</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.183</t>
+          <t>3786.38739355488</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.893</t>
+          <t>4277.64375246507</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>4821.11516570349</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>5026.92452903273</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.373</t>
+          <t>4407.12130256491</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1978.1820783021</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2005.18503207527</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2168.92671235542</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2260.62913280164</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2155.34210301008</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2358.82577089619</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2495.2515529011</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2672.68244677767</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2870.10050861952</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>3131.02360572584</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>3435.76932676861</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>3880.8857756492</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>4346.26195458432</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>4509.60466212511</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>3940.57773726773</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1165.6866785482</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1572.66633236716</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1736.40228629764</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2030.64796005739</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2215.73513655915</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2216.67441116309</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2514.37200073204</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2965.13686101886</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>3930.62225270929</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>4592.5542240151</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>5562.65861509087</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>6549.87071177545</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>7779.41870294098</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>7393.65003141043</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>5275.21784505622</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1102698335.57299</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1071375723.00998</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1064046584.46363</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1038061970.02459</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>992221810.700474</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>975925914</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>995819565.683451</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1009110983</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1022754578</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1018847478.2451</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1073443327</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1141254371</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1140254722.30617</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1141368776</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>952964600.63245</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1229996614.94619</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1202231511.84761</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1197108626.34275</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1175735691.08207</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1121585837.85306</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1108907704</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1114127481.65549</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1127773589</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1148490171</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1152113319.26823</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1185772206</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1259874378</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1271582452.36758</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1270919798.47214</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1097815928.62376</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>782101882.575398</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>753133465.081181</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>740618963.206468</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>715843237.034939</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>666321602.174527</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>644288038.902677</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>654892049.058957</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>650316806.699255</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>680698141.005312</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>701440081.865048</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>696057363.171713</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>738433067.071925</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>751381285.466012</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>736418564.598609</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>610324795.603824</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>633300</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>619300</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>617200</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>606300</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>579200</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>572500</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>577699.999832412</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>585300</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>594000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>595300.000127613</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>607700</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>646000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>655600.000094429</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>660424.806154005</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>614162.221545645</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>589900</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>573000</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>568500</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>554400</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>529700</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>520800</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>529799.999845246</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>538300.000508112</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>541700</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>537899.999595459</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>558600</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>594899.999484977</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>597100.00008625</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>606000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>546930.555416823</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1229996614.94619</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1202231511.84761</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1197108626.34275</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1175735691.08207</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1121585837.85306</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1108907704</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1114127481.65549</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1127773589</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1148490171</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1152113319.26823</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1185772206</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1259874378</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1271582452.36758</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1270919798.47214</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1097815928.62376</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1102698335.57299</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1071375723.00998</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1064046584.46363</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1038061970.02459</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>992221810.700474</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>975925914</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>995819565.683451</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1009110983</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1022754578</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1018847478.2451</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1073443327</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1141254371</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1140254722.30617</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1141368776</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>952964600.63245</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.432957307584914</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.424290485280814</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.414244980080208</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.401835231658574</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.391720262374542</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.396275348473721</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.391932582665419</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.39465875502121</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.358943598706702</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.396037207919124</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.41643028720111</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.409067485883032</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.38331425702095</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.372967861503811</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.389717279509351</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.495833562839275</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.505335916986218</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.507567636861314</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.510313637691528</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.530444633195852</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.529587032593355</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.534578002160968</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.533321226370326</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.532121704033019</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.525422647058035</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.511536690506456</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.506614254744889</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.530096368124594</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.527774495260558</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.523574013489296</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0712091295758107</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.0703735977329677</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.0781873830584773</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0878511306498983</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0778351044296063</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0741376189329238</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0734894151736126</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.072020018608464</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.108934697260279</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0785401450228414</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0720330222924337</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0843182593720788</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0865893748544551</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0992576432356307</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0867087070013527</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.312193990390098</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.307799396730762</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.297775294325577</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.28689935380008</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.279698251361371</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.283787914224018</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.285719455533138</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.292066846754811</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.28539735666268</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.299631050602165</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.317499404467549</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.313093618797607</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.313726742537568</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.317492685976851</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.330632029949086</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.581542571932428</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.588639190261022</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.588409307670143</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.587257231156354</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.60768719805086</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.60760353311715</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.60792014362135</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.60472423075156</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.600160104455164</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.593090372720958</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.585145653993799</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.576657993504508</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.586727142569739</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.579775338458534</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.576241107211232</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.106263437677474</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.103561413008215</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.11381539800428</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.125843415043567</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.112614550587768</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.108608552658832</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.106360400845511</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.103208922493629</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.114442538882156</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.107278576676877</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0973549415386524</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.110248387697885</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.099546114892692</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.102731975564615</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0931268628396821</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>8283.83643</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>9788.73997</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>10859.83237</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>12316.32551</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>12179.36035</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>12772.51023</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>14048.57844</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>16424.78141</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>21205.70703</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>26063.58469</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>30167.77286</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>35532.43521</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>44246.99087</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>48445.03863</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>37266.24415</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3328.88604</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4171.19585</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>4422.00556</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>4982.86686</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>5140.18771</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>5090.12008</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5563.42507</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>6535.17728</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>8804.27792</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>10653.95152</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>12322.90053</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>14775.72882</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>18971.75527</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>21047.2485</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>16677.98605</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>11036.205760143</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>11537.7600611927</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>12212.6441979157</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>13076.9889229306</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>13676.9054056121</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>14428.9055271773</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>15261.1881713661</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>16381.5870515466</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>17761.4481197441</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>19174.1289286297</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>20828.4374679303</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>22974.5590393707</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>25135.2373466103</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>26689.8456049247</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>27213.4780317637</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
